--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104762_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104762_W34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4599</v>
+        <v>4.7596</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1748</v>
+        <v>6.0039</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7148</v>
+        <v>-1.2444</v>
       </c>
       <c r="G2" t="n">
         <v>5.0012</v>
@@ -610,13 +610,13 @@
         <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9966</v>
+        <v>0.3031</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8364</v>
+        <v>-0.0073</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1601</v>
+        <v>0.3104</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5447</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0651</v>
+        <v>3.5843</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7015</v>
+        <v>4.9384</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6364</v>
+        <v>-1.3541</v>
       </c>
       <c r="G3" t="n">
         <v>3.3463</v>
@@ -688,13 +688,13 @@
         <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0536</v>
+        <v>0.4656</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1623</v>
+        <v>0.3992</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2159</v>
+        <v>0.0664</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7117</v>
+        <v>3.4608</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9399</v>
+        <v>6.5322</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.2282</v>
+        <v>-3.0713</v>
       </c>
       <c r="G4" t="n">
         <v>2.907</v>
@@ -766,13 +766,13 @@
         <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4716</v>
+        <v>0.2775</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0468</v>
+        <v>0.5454</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4248</v>
+        <v>-0.268</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0895</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3095</v>
+        <v>2.4239</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0367</v>
+        <v>2.5618</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7272</v>
+        <v>-0.1379</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8352000000000001</v>
+        <v>0.2881</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3205</v>
+        <v>-0.1202</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1557</v>
+        <v>0.4083</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7146</v>
+        <v>3.31</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8953</v>
+        <v>0.9718</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8192</v>
+        <v>2.3383</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5497</v>
+        <v>-3.0219</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5749</v>
+        <v>-1.092</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9749</v>
+        <v>-1.93</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4553</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5934</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9367</v>
+        <v>0.9977</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4603</v>
+        <v>0.3899</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4764</v>
+        <v>0.6077</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2472</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.082</v>
+        <v>1.6569</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2288</v>
+        <v>0.9919</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8532</v>
+        <v>0.665</v>
       </c>
       <c r="G6" t="n">
         <v>1.2643</v>
@@ -922,13 +922,13 @@
         <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8177</v>
+        <v>0.3926</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3714</v>
+        <v>0.1345</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4463</v>
+        <v>0.2581</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7586</v>
+        <v>0.3203</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6142</v>
+        <v>2.1415</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1444</v>
+        <v>-1.8213</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2881</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1202</v>
+        <v>0.3205</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4083</v>
+        <v>-1.1557</v>
       </c>
       <c r="J7" t="n">
-        <v>3.31</v>
+        <v>1.7146</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9718</v>
+        <v>0.8953</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3383</v>
+        <v>0.8192</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0219</v>
+        <v>-2.5497</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.092</v>
+        <v>-0.5749</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.93</v>
+        <v>-1.9749</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1382</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2763</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3324</v>
+        <v>1.9474</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5576</v>
+        <v>1.5651</v>
       </c>
       <c r="U7" t="n">
-        <v>0.89</v>
+        <v>0.3823</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>J. TABOADA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6599</v>
+        <v>0.1413</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2766</v>
+        <v>0.262</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6167</v>
+        <v>-0.1207</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.317</v>
+        <v>-0.6855</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3144</v>
+        <v>-0.5455</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0026</v>
+        <v>-0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6254</v>
+        <v>1.0774</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8488</v>
+        <v>0.6755</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2234</v>
+        <v>0.4019</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6916</v>
+        <v>-1.7629</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4656</v>
+        <v>-1.221</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.226</v>
+        <v>-0.5419</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9105</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9105</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6795</v>
+        <v>0.6886</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8126</v>
+        <v>0.3227</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8669</v>
+        <v>0.3659</v>
       </c>
       <c r="V8" t="n">
-        <v>0.387</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7025</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. TABOADA</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0402</v>
+        <v>-0.2696</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3804</v>
+        <v>-1.0859</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3402</v>
+        <v>0.8163</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6855</v>
+        <v>-2.9857</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5455</v>
+        <v>-3.6766</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.14</v>
+        <v>0.6909</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0774</v>
+        <v>-1.8825</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6755</v>
+        <v>-1.8518</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4019</v>
+        <v>-0.0307</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7629</v>
+        <v>-1.1032</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.221</v>
+        <v>-1.8248</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5419</v>
+        <v>0.7215</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6829</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8211</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5875</v>
+        <v>0.0803</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4411</v>
+        <v>-0.2442</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1464</v>
+        <v>0.3245</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5447</v>
+        <v>2.4082</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5447</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5796</v>
+        <v>-0.2844</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6781</v>
+        <v>0.8028</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0986</v>
+        <v>-1.0872</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9857</v>
+        <v>-2.317</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.6766</v>
+        <v>-2.3144</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6909</v>
+        <v>-0.0026</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8825</v>
+        <v>-0.6254</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8518</v>
+        <v>-0.8488</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0307</v>
+        <v>0.2234</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1032</v>
+        <v>-1.6916</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8248</v>
+        <v>-1.4656</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7215</v>
+        <v>-0.226</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2276</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3658</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2296</v>
+        <v>0.7352</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8364</v>
+        <v>0.3388</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6068</v>
+        <v>0.3964</v>
       </c>
       <c r="V10" t="n">
-        <v>2.4082</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1789</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2292</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1524</v>
+        <v>-1.0339</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2905</v>
+        <v>-0.1721</v>
       </c>
       <c r="F11" t="n">
         <v>-0.8618</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.1184</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0697</v>
+        <v>0.0487</v>
       </c>
       <c r="U11" t="n">
         <v>0.0697</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0454</v>
+        <v>-2.4007</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2346</v>
+        <v>-0.1207</v>
       </c>
       <c r="F12" t="n">
         <v>-2.28</v>
@@ -1390,10 +1390,10 @@
         <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4738</v>
+        <v>0.1184</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3714</v>
+        <v>0.0161</v>
       </c>
       <c r="U12" t="n">
         <v>0.1024</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1699</v>
+        <v>-4.2186</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6785</v>
+        <v>-2.9154</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4914</v>
+        <v>-1.3032</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3183</v>
@@ -1468,13 +1468,13 @@
         <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2865</v>
+        <v>1.2378</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1611</v>
+        <v>0.9242</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1255</v>
+        <v>0.3137</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5447</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.1396</v>
+        <v>8.139899999999999</v>
       </c>
       <c r="E14" t="n">
         <v>19.9404</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.8005</v>
+        <v>-11.8006</v>
       </c>
       <c r="G14" t="n">
         <v>-0.008000000000000451</v>
@@ -1516,13 +1516,13 @@
         <v>-6.8901</v>
       </c>
       <c r="I14" t="n">
-        <v>6.882199999999997</v>
+        <v>6.882200000000001</v>
       </c>
       <c r="J14" t="n">
         <v>23.5599</v>
       </c>
       <c r="K14" t="n">
-        <v>5.897699999999999</v>
+        <v>5.897700000000001</v>
       </c>
       <c r="L14" t="n">
         <v>17.6622</v>
@@ -1546,13 +1546,13 @@
         <v>15.9344</v>
       </c>
       <c r="S14" t="n">
-        <v>7.3627</v>
+        <v>7.3626</v>
       </c>
       <c r="T14" t="n">
-        <v>4.433299999999999</v>
+        <v>4.4331</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9296</v>
+        <v>2.9295</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4911</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8374</v>
+        <v>2.1441</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4391</v>
+        <v>2.9653</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6017</v>
+        <v>-0.8213</v>
       </c>
       <c r="G15" t="n">
         <v>1.991</v>
@@ -1624,13 +1624,13 @@
         <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2902</v>
+        <v>-0.9835</v>
       </c>
       <c r="T15" t="n">
-        <v>0.232</v>
+        <v>-0.2418</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5222</v>
+        <v>-0.7418</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2292</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>J. PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4668</v>
+        <v>1.9764</v>
       </c>
       <c r="E16" t="n">
-        <v>3.766</v>
+        <v>3.9889</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2993</v>
+        <v>-2.0125</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6211</v>
+        <v>3.0906</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1024</v>
+        <v>1.9529</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5187</v>
+        <v>1.1377</v>
       </c>
       <c r="J16" t="n">
-        <v>5.9743</v>
+        <v>5.8978</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3677</v>
+        <v>2.8301</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6066</v>
+        <v>3.0677</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.3531</v>
+        <v>-2.8072</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2653</v>
+        <v>-0.8772</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0879</v>
+        <v>-1.93</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5039</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.5526</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
         <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7154</v>
+        <v>-0.6573</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7102000000000001</v>
+        <v>-0.4928</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0052</v>
+        <v>-0.1645</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6342</v>
+        <v>-0.2292</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6342</v>
+        <v>0.8603</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PEREZ</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8023</v>
+        <v>1.4494</v>
       </c>
       <c r="E17" t="n">
-        <v>3.752</v>
+        <v>2.9369</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9497</v>
+        <v>-1.4875</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0906</v>
+        <v>2.6211</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9529</v>
+        <v>2.1024</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1377</v>
+        <v>0.5187</v>
       </c>
       <c r="J17" t="n">
-        <v>5.8978</v>
+        <v>5.9743</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8301</v>
+        <v>3.3677</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0677</v>
+        <v>2.6066</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8072</v>
+        <v>-3.3531</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8772</v>
+        <v>-1.2653</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.93</v>
+        <v>-2.0879</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2276</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2763</v>
+        <v>-4.5526</v>
       </c>
       <c r="R17" t="n">
         <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8315</v>
+        <v>-0.302</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7297</v>
+        <v>-0.1189</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1018</v>
+        <v>-0.183</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2292</v>
+        <v>1.6342</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8603</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3452</v>
+        <v>-0.1599</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0333</v>
+        <v>2.5595</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6881</v>
+        <v>-2.7194</v>
       </c>
       <c r="G18" t="n">
         <v>0.8413</v>
@@ -1858,13 +1858,13 @@
         <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3461</v>
+        <v>-0.159</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6502</v>
+        <v>0.1765</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3041</v>
+        <v>-0.3355</v>
       </c>
       <c r="V18" t="n">
         <v>-0.387</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6282</v>
+        <v>-1.2101</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4614</v>
+        <v>2.8168</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.0896</v>
+        <v>-4.0269</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2148</v>
@@ -1936,13 +1936,13 @@
         <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5516</v>
+        <v>-1.1335</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8691</v>
+        <v>-0.5138</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6825</v>
+        <v>-0.6198</v>
       </c>
       <c r="V19" t="n">
         <v>0.5447</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7439</v>
+        <v>-1.5314</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.612</v>
+        <v>-0.4936</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1319</v>
+        <v>-1.0378</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4211</v>
@@ -2014,13 +2014,13 @@
         <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0057</v>
+        <v>-0.7932</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2788</v>
+        <v>-0.1604</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7269</v>
+        <v>-0.6328</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0031</v>
+        <v>-1.7418</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7255</v>
+        <v>1.0808</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7286</v>
+        <v>-2.8227</v>
       </c>
       <c r="G21" t="n">
         <v>1.1258</v>
@@ -2092,13 +2092,13 @@
         <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0103</v>
+        <v>-0.7491</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3812</v>
+        <v>-0.0258</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6291</v>
+        <v>-0.7232</v>
       </c>
       <c r="V21" t="n">
         <v>0.1578</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2107</v>
+        <v>-2.0365</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.082</v>
+        <v>-0.8451</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1287</v>
+        <v>-1.1914</v>
       </c>
       <c r="G22" t="n">
         <v>-1.47</v>
@@ -2170,13 +2170,13 @@
         <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1473</v>
+        <v>-0.9732</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0455</v>
+        <v>-0.8087</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1018</v>
+        <v>-0.1645</v>
       </c>
       <c r="V22" t="n">
         <v>1.0895</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4478</v>
+        <v>-2.0471</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3547</v>
+        <v>-2.2363</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0931</v>
+        <v>0.1892</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2018</v>
@@ -2248,13 +2248,13 @@
         <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1079</v>
+        <v>-0.7071</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3485</v>
+        <v>-0.2301</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7594</v>
+        <v>-0.4771</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5577</v>
+        <v>-4.9828</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.328</v>
+        <v>-0.9727</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2297</v>
+        <v>-4.0101</v>
       </c>
       <c r="G24" t="n">
         <v>-4.3543</v>
@@ -2326,13 +2326,13 @@
         <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4797</v>
+        <v>-0.9048</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8691</v>
+        <v>-0.5138</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6106</v>
+        <v>-0.391</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0895</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.139700000000001</v>
+        <v>-8.139699999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>11.8006</v>
+        <v>11.8005</v>
       </c>
       <c r="F25" t="n">
         <v>-19.9404</v>
@@ -2404,13 +2404,13 @@
         <v>13.658</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.3627</v>
+        <v>-7.362699999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.9295</v>
+        <v>-2.929600000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.4332</v>
+        <v>-4.433199999999999</v>
       </c>
       <c r="V25" t="n">
         <v>1.4913</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104762_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104762_W34.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.0963</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104762_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-5.6052</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
